--- a/artfynd/A 49239-2024 artfynd.xlsx
+++ b/artfynd/A 49239-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127103028</v>
       </c>
       <c r="B2" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>127103027</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>127102987</v>
       </c>
       <c r="B5" t="n">
-        <v>97239</v>
+        <v>97314</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>127102995</v>
       </c>
       <c r="B7" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127102964</v>
+        <v>127102960</v>
       </c>
       <c r="B8" t="n">
         <v>57657</v>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591595</v>
+        <v>591616</v>
       </c>
       <c r="R8" t="n">
-        <v>6985510</v>
+        <v>6985492</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,7 +1374,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127102960</v>
+        <v>127102964</v>
       </c>
       <c r="B9" t="n">
         <v>57657</v>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591616</v>
+        <v>591595</v>
       </c>
       <c r="R9" t="n">
-        <v>6985492</v>
+        <v>6985510</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 49239-2024 artfynd.xlsx
+++ b/artfynd/A 49239-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127103028</v>
       </c>
       <c r="B2" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>127103027</v>
       </c>
       <c r="B4" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>127102987</v>
       </c>
       <c r="B5" t="n">
-        <v>97314</v>
+        <v>97320</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>127102995</v>
       </c>
       <c r="B7" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 49239-2024 artfynd.xlsx
+++ b/artfynd/A 49239-2024 artfynd.xlsx
@@ -974,7 +974,7 @@
         <v>127102987</v>
       </c>
       <c r="B5" t="n">
-        <v>97320</v>
+        <v>97321</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49239-2024 artfynd.xlsx
+++ b/artfynd/A 49239-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127103028</v>
+        <v>127102957</v>
       </c>
       <c r="B2" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591626</v>
+        <v>591568</v>
       </c>
       <c r="R2" t="n">
-        <v>6985495</v>
+        <v>6985550</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127102957</v>
+        <v>127103028</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591568</v>
+        <v>591626</v>
       </c>
       <c r="R3" t="n">
-        <v>6985550</v>
+        <v>6985495</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 49239-2024 artfynd.xlsx
+++ b/artfynd/A 49239-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127102957</v>
+        <v>127103028</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591568</v>
+        <v>591626</v>
       </c>
       <c r="R2" t="n">
-        <v>6985550</v>
+        <v>6985495</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127103028</v>
+        <v>127102957</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591626</v>
+        <v>591568</v>
       </c>
       <c r="R3" t="n">
-        <v>6985495</v>
+        <v>6985550</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1984,6 +1984,593 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127465995</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80117</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>591676</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6985520</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127465980</v>
+      </c>
+      <c r="B16" t="n">
+        <v>75138</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>591628</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6985578</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127465997</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91322</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>591582</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6985623</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127465990</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>591572</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6985620</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127466010</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>591546</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6985624</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127466009</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>591588</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6985610</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49239-2024 artfynd.xlsx
+++ b/artfynd/A 49239-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127103028</v>
       </c>
       <c r="B2" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127102957</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -874,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127103027</v>
+        <v>127102987</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>97325</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591692</v>
+        <v>591647</v>
       </c>
       <c r="R4" t="n">
-        <v>6985539</v>
+        <v>6985572</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127102987</v>
+        <v>127103027</v>
       </c>
       <c r="B5" t="n">
-        <v>97321</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591647</v>
+        <v>591692</v>
       </c>
       <c r="R5" t="n">
-        <v>6985572</v>
+        <v>6985539</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
         <v>127099400</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>127102995</v>
       </c>
       <c r="B7" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>127102960</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>127102964</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>127102956</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>127102958</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>127102962</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>127102959</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>127102963</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>127465995</v>
       </c>
       <c r="B15" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>127465980</v>
       </c>
       <c r="B16" t="n">
-        <v>75138</v>
+        <v>75142</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>127465997</v>
       </c>
       <c r="B17" t="n">
-        <v>91322</v>
+        <v>91326</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>127465990</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>127466010</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>127466009</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 49239-2024 artfynd.xlsx
+++ b/artfynd/A 49239-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127103028</v>
+        <v>127102957</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591626</v>
+        <v>591568</v>
       </c>
       <c r="R2" t="n">
-        <v>6985495</v>
+        <v>6985550</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127102957</v>
+        <v>127103028</v>
       </c>
       <c r="B3" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591568</v>
+        <v>591626</v>
       </c>
       <c r="R3" t="n">
-        <v>6985550</v>
+        <v>6985495</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127102987</v>
+        <v>127103027</v>
       </c>
       <c r="B4" t="n">
-        <v>97325</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591647</v>
+        <v>591692</v>
       </c>
       <c r="R4" t="n">
-        <v>6985572</v>
+        <v>6985539</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127103027</v>
+        <v>127102987</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>97325</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591692</v>
+        <v>591647</v>
       </c>
       <c r="R5" t="n">
-        <v>6985539</v>
+        <v>6985572</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 49239-2024 artfynd.xlsx
+++ b/artfynd/A 49239-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127102957</v>
+        <v>127103028</v>
       </c>
       <c r="B2" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591568</v>
+        <v>591626</v>
       </c>
       <c r="R2" t="n">
-        <v>6985550</v>
+        <v>6985495</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127103028</v>
+        <v>127102957</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591626</v>
+        <v>591568</v>
       </c>
       <c r="R3" t="n">
-        <v>6985495</v>
+        <v>6985550</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 49239-2024 artfynd.xlsx
+++ b/artfynd/A 49239-2024 artfynd.xlsx
@@ -874,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127103027</v>
+        <v>127102987</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>97325</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591692</v>
+        <v>591647</v>
       </c>
       <c r="R4" t="n">
-        <v>6985539</v>
+        <v>6985572</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127102987</v>
+        <v>127103027</v>
       </c>
       <c r="B5" t="n">
-        <v>97325</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591647</v>
+        <v>591692</v>
       </c>
       <c r="R5" t="n">
-        <v>6985572</v>
+        <v>6985539</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 49239-2024 artfynd.xlsx
+++ b/artfynd/A 49239-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127103028</v>
+        <v>127102957</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591626</v>
+        <v>591568</v>
       </c>
       <c r="R2" t="n">
-        <v>6985495</v>
+        <v>6985550</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127102957</v>
+        <v>127103028</v>
       </c>
       <c r="B3" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591568</v>
+        <v>591626</v>
       </c>
       <c r="R3" t="n">
-        <v>6985550</v>
+        <v>6985495</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,7 +877,7 @@
         <v>127102987</v>
       </c>
       <c r="B4" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>127103027</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>127099400</v>
       </c>
       <c r="B6" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>127102995</v>
       </c>
       <c r="B7" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127102960</v>
+        <v>127102964</v>
       </c>
       <c r="B8" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591616</v>
+        <v>591595</v>
       </c>
       <c r="R8" t="n">
-        <v>6985492</v>
+        <v>6985510</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127102964</v>
+        <v>127102960</v>
       </c>
       <c r="B9" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591595</v>
+        <v>591616</v>
       </c>
       <c r="R9" t="n">
-        <v>6985510</v>
+        <v>6985492</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1479,7 +1479,7 @@
         <v>127102956</v>
       </c>
       <c r="B10" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>127102958</v>
       </c>
       <c r="B11" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>127102962</v>
       </c>
       <c r="B12" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>127102959</v>
       </c>
       <c r="B13" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>127102963</v>
       </c>
       <c r="B14" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>127465995</v>
       </c>
       <c r="B15" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>127465980</v>
       </c>
       <c r="B16" t="n">
-        <v>75142</v>
+        <v>75144</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>127465997</v>
       </c>
       <c r="B17" t="n">
-        <v>91326</v>
+        <v>91328</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>127465990</v>
       </c>
       <c r="B18" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>127466010</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>127466009</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 49239-2024 artfynd.xlsx
+++ b/artfynd/A 49239-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127102957</v>
+        <v>127103028</v>
       </c>
       <c r="B2" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591568</v>
+        <v>591626</v>
       </c>
       <c r="R2" t="n">
-        <v>6985550</v>
+        <v>6985495</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127103028</v>
+        <v>127102957</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591626</v>
+        <v>591568</v>
       </c>
       <c r="R3" t="n">
-        <v>6985495</v>
+        <v>6985550</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127102987</v>
+        <v>127103027</v>
       </c>
       <c r="B4" t="n">
-        <v>97327</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591647</v>
+        <v>591692</v>
       </c>
       <c r="R4" t="n">
-        <v>6985572</v>
+        <v>6985539</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127103027</v>
+        <v>127102987</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>97327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591692</v>
+        <v>591647</v>
       </c>
       <c r="R5" t="n">
-        <v>6985539</v>
+        <v>6985572</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1272,7 +1272,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127102964</v>
+        <v>127102960</v>
       </c>
       <c r="B8" t="n">
         <v>57663</v>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591595</v>
+        <v>591616</v>
       </c>
       <c r="R8" t="n">
-        <v>6985510</v>
+        <v>6985492</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,7 +1374,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127102960</v>
+        <v>127102964</v>
       </c>
       <c r="B9" t="n">
         <v>57663</v>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591616</v>
+        <v>591595</v>
       </c>
       <c r="R9" t="n">
-        <v>6985492</v>
+        <v>6985510</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 49239-2024 artfynd.xlsx
+++ b/artfynd/A 49239-2024 artfynd.xlsx
@@ -1272,7 +1272,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127102960</v>
+        <v>127102964</v>
       </c>
       <c r="B8" t="n">
         <v>57663</v>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591616</v>
+        <v>591595</v>
       </c>
       <c r="R8" t="n">
-        <v>6985492</v>
+        <v>6985510</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,7 +1374,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127102964</v>
+        <v>127102960</v>
       </c>
       <c r="B9" t="n">
         <v>57663</v>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591595</v>
+        <v>591616</v>
       </c>
       <c r="R9" t="n">
-        <v>6985510</v>
+        <v>6985492</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 49239-2024 artfynd.xlsx
+++ b/artfynd/A 49239-2024 artfynd.xlsx
@@ -974,7 +974,7 @@
         <v>127102987</v>
       </c>
       <c r="B5" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127102964</v>
+        <v>127102960</v>
       </c>
       <c r="B8" t="n">
         <v>57663</v>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591595</v>
+        <v>591616</v>
       </c>
       <c r="R8" t="n">
-        <v>6985510</v>
+        <v>6985492</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,7 +1374,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127102960</v>
+        <v>127102964</v>
       </c>
       <c r="B9" t="n">
         <v>57663</v>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591616</v>
+        <v>591595</v>
       </c>
       <c r="R9" t="n">
-        <v>6985492</v>
+        <v>6985510</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2183,7 +2183,7 @@
         <v>127465997</v>
       </c>
       <c r="B17" t="n">
-        <v>91328</v>
+        <v>91334</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 49239-2024 artfynd.xlsx
+++ b/artfynd/A 49239-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127103028</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127102957</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>127103027</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>127102987</v>
       </c>
       <c r="B5" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>127099400</v>
       </c>
       <c r="B6" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>127102995</v>
       </c>
       <c r="B7" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127102960</v>
+        <v>127102956</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591616</v>
+        <v>591570</v>
       </c>
       <c r="R8" t="n">
-        <v>6985492</v>
+        <v>6985542</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1377,7 +1377,7 @@
         <v>127102964</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127102956</v>
+        <v>127102960</v>
       </c>
       <c r="B10" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591570</v>
+        <v>591616</v>
       </c>
       <c r="R10" t="n">
-        <v>6985542</v>
+        <v>6985492</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1581,7 +1581,7 @@
         <v>127102958</v>
       </c>
       <c r="B11" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>127102962</v>
       </c>
       <c r="B12" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>127102959</v>
       </c>
       <c r="B13" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>127102963</v>
       </c>
       <c r="B14" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>127465995</v>
       </c>
       <c r="B15" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>127465980</v>
       </c>
       <c r="B16" t="n">
-        <v>75144</v>
+        <v>75147</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>127465997</v>
       </c>
       <c r="B17" t="n">
-        <v>91334</v>
+        <v>91337</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>127465990</v>
       </c>
       <c r="B18" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>127466010</v>
       </c>
       <c r="B19" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>127466009</v>
       </c>
       <c r="B20" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 49239-2024 artfynd.xlsx
+++ b/artfynd/A 49239-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127103028</v>
+        <v>127102957</v>
       </c>
       <c r="B2" t="n">
-        <v>79023</v>
+        <v>57672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591626</v>
+        <v>591568</v>
       </c>
       <c r="R2" t="n">
-        <v>6985495</v>
+        <v>6985550</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127102957</v>
+        <v>127103028</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591568</v>
+        <v>591626</v>
       </c>
       <c r="R3" t="n">
-        <v>6985550</v>
+        <v>6985495</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,7 +877,7 @@
         <v>127103027</v>
       </c>
       <c r="B4" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>127102987</v>
       </c>
       <c r="B5" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>127099400</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>127102995</v>
       </c>
       <c r="B7" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127102956</v>
+        <v>127102964</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591570</v>
+        <v>591595</v>
       </c>
       <c r="R8" t="n">
-        <v>6985542</v>
+        <v>6985510</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127102964</v>
+        <v>127102960</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591595</v>
+        <v>591616</v>
       </c>
       <c r="R9" t="n">
-        <v>6985510</v>
+        <v>6985492</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1476,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127102960</v>
+        <v>127102956</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591616</v>
+        <v>591570</v>
       </c>
       <c r="R10" t="n">
-        <v>6985492</v>
+        <v>6985542</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1581,7 +1581,7 @@
         <v>127102958</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>127102962</v>
       </c>
       <c r="B12" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>127102959</v>
       </c>
       <c r="B13" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>127102963</v>
       </c>
       <c r="B14" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>127465995</v>
       </c>
       <c r="B15" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>127465980</v>
       </c>
       <c r="B16" t="n">
-        <v>75147</v>
+        <v>75153</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>127465997</v>
       </c>
       <c r="B17" t="n">
-        <v>91337</v>
+        <v>91345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>127465990</v>
       </c>
       <c r="B18" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>127466010</v>
       </c>
       <c r="B19" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>127466009</v>
       </c>
       <c r="B20" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 49239-2024 artfynd.xlsx
+++ b/artfynd/A 49239-2024 artfynd.xlsx
@@ -2183,7 +2183,7 @@
         <v>127465997</v>
       </c>
       <c r="B17" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 49239-2024 artfynd.xlsx
+++ b/artfynd/A 49239-2024 artfynd.xlsx
@@ -2183,7 +2183,7 @@
         <v>127465997</v>
       </c>
       <c r="B17" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 49239-2024 artfynd.xlsx
+++ b/artfynd/A 49239-2024 artfynd.xlsx
@@ -2183,7 +2183,7 @@
         <v>127465997</v>
       </c>
       <c r="B17" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 49239-2024 artfynd.xlsx
+++ b/artfynd/A 49239-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2571,6 +2571,614 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129431317</v>
+      </c>
+      <c r="B21" t="n">
+        <v>56917</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>591619</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6985503</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129431283</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>591694</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6985537</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129431316</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>591614</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6985599</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129431318</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80148</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>591675</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6985511</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129431284</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>591661</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6985470</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129431319</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80148</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>591705</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6985507</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49239-2024 artfynd.xlsx
+++ b/artfynd/A 49239-2024 artfynd.xlsx
@@ -2888,7 +2888,7 @@
         <v>129431318</v>
       </c>
       <c r="B24" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>129431319</v>
       </c>
       <c r="B26" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 49239-2024 artfynd.xlsx
+++ b/artfynd/A 49239-2024 artfynd.xlsx
@@ -2576,7 +2576,7 @@
         <v>129431317</v>
       </c>
       <c r="B21" t="n">
-        <v>56917</v>
+        <v>56920</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>129431283</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>129431316</v>
       </c>
       <c r="B23" t="n">
-        <v>57740</v>
+        <v>57743</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>129431318</v>
       </c>
       <c r="B24" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>129431284</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>129431319</v>
       </c>
       <c r="B26" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
